--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_3.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02158134424323</v>
+        <v>0.0114485810113519</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008417747105701008</v>
+        <v>0.008404691819872865</v>
       </c>
       <c r="C2" t="n">
-        <v>18938934</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18938934</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>13451420</v>
+        <v>4662961</v>
       </c>
       <c r="L2" t="n">
-        <v>7553975</v>
+        <v>2703203</v>
       </c>
       <c r="M2" t="n">
-        <v>1756383</v>
+        <v>641723</v>
       </c>
       <c r="N2" t="n">
-        <v>60539</v>
+        <v>20763</v>
       </c>
       <c r="O2" t="n">
-        <v>1044761</v>
+        <v>372353</v>
       </c>
       <c r="P2" t="n">
-        <v>408894</v>
+        <v>140537</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999932050704956</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8799209594726562</v>
+        <v>0.9050005674362183</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7544624805450439</v>
+        <v>0.8093584775924683</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6871532797813416</v>
+        <v>0.7510961294174194</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2015722543001175</v>
+        <v>0.2151829153299332</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7411386966705322</v>
+        <v>0.7925557494163513</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8444140553474426</v>
+        <v>0.8977762460708618</v>
       </c>
       <c r="X2" t="n">
-        <v>18938934</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>18938934</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>14462079</v>
+        <v>4849843</v>
       </c>
       <c r="AG2" t="n">
-        <v>8899088</v>
+        <v>2984316</v>
       </c>
       <c r="AH2" t="n">
-        <v>2397713</v>
+        <v>801097</v>
       </c>
       <c r="AI2" t="n">
-        <v>176916</v>
+        <v>59133</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1376789</v>
+        <v>459291</v>
       </c>
       <c r="AK2" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566799402236938</v>
+        <v>0.9567072987556458</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112439155578613</v>
+        <v>0.9112796187400818</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581776022911072</v>
+        <v>0.8579719662666321</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6626315712928772</v>
+        <v>0.6624432802200317</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020464420318604</v>
+        <v>0.9019978642463684</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314221143722534</v>
+        <v>0.9314266443252563</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.005080699936178246</v>
+        <v>0.002549237908072045</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002018670822238358</v>
+        <v>0.002014117820993523</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>13451420</v>
+        <v>4662961</v>
       </c>
       <c r="E3" t="n">
-        <v>1627616</v>
+        <v>398405</v>
       </c>
       <c r="F3" t="n">
-        <v>19598</v>
+        <v>2516</v>
       </c>
       <c r="G3" t="n">
-        <v>2023</v>
+        <v>399</v>
       </c>
       <c r="H3" t="n">
-        <v>1014</v>
+        <v>119</v>
       </c>
       <c r="I3" t="n">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>30049737</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>32051404</v>
+        <v>10862111</v>
       </c>
       <c r="L3" t="n">
-        <v>36751520</v>
+        <v>12500159</v>
       </c>
       <c r="M3" t="n">
-        <v>45393869</v>
+        <v>15269276</v>
       </c>
       <c r="N3" t="n">
-        <v>48481807</v>
+        <v>16250939</v>
       </c>
       <c r="O3" t="n">
-        <v>47096955</v>
+        <v>15809141</v>
       </c>
       <c r="P3" t="n">
-        <v>48333614</v>
+        <v>16206697</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.890720009803772</v>
+        <v>0.9207313656806946</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7724799513816833</v>
+        <v>0.8243706822395325</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6283375024795532</v>
+        <v>0.687021791934967</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2265698164701462</v>
+        <v>0.2324199080467224</v>
       </c>
       <c r="V3" t="n">
-        <v>0.684220552444458</v>
+        <v>0.7309653162956238</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7051768898963928</v>
+        <v>0.7270371317863464</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14462079</v>
+        <v>4849843</v>
       </c>
       <c r="Z3" t="n">
-        <v>593526</v>
+        <v>199096</v>
       </c>
       <c r="AA3" t="n">
-        <v>25572</v>
+        <v>8579</v>
       </c>
       <c r="AB3" t="n">
-        <v>20336</v>
+        <v>6817</v>
       </c>
       <c r="AC3" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>30049866</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>33232195</v>
+        <v>11132126</v>
       </c>
       <c r="AG3" t="n">
-        <v>38343158</v>
+        <v>12846342</v>
       </c>
       <c r="AH3" t="n">
-        <v>45797268</v>
+        <v>15349322</v>
       </c>
       <c r="AI3" t="n">
-        <v>48631528</v>
+        <v>16296534</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47312358</v>
+        <v>15856699</v>
       </c>
       <c r="AK3" t="n">
-        <v>48369192</v>
+        <v>16209445</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576433300971985</v>
+        <v>0.9576323628425598</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.910033106803894</v>
+        <v>0.9100990891456604</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8577702045440674</v>
+        <v>0.8576458692550659</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.662115752696991</v>
+        <v>0.6619316339492798</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016677737236023</v>
+        <v>0.901633083820343</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313610792160034</v>
+        <v>0.9313350915908813</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0569206679450853</v>
+        <v>0.0394925059731625</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03186393749853683</v>
+        <v>0.03182526122067923</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1733527</v>
+        <v>458460</v>
       </c>
       <c r="E4" t="n">
-        <v>7553975</v>
+        <v>2703203</v>
       </c>
       <c r="F4" t="n">
-        <v>447271</v>
+        <v>111214</v>
       </c>
       <c r="G4" t="n">
-        <v>16686</v>
+        <v>2669</v>
       </c>
       <c r="H4" t="n">
-        <v>25459</v>
+        <v>3355</v>
       </c>
       <c r="I4" t="n">
-        <v>1943</v>
+        <v>209</v>
       </c>
       <c r="J4" t="n">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>1835658</v>
+        <v>489479</v>
       </c>
       <c r="L4" t="n">
-        <v>2458418</v>
+        <v>636730</v>
       </c>
       <c r="M4" t="n">
-        <v>799645</v>
+        <v>212659</v>
       </c>
       <c r="N4" t="n">
-        <v>239795</v>
+        <v>75727</v>
       </c>
       <c r="O4" t="n">
-        <v>364909</v>
+        <v>97460</v>
       </c>
       <c r="P4" t="n">
-        <v>75340</v>
+        <v>16002</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999966025352478</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8852875828742981</v>
+        <v>0.9127981662750244</v>
       </c>
       <c r="S4" t="n">
-        <v>0.763364851474762</v>
+        <v>0.8167955875396729</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6564306020736694</v>
+        <v>0.7176315188407898</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2133412808179855</v>
+        <v>0.2234695255756378</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7115431427955627</v>
+        <v>0.760515570640564</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7685399055480957</v>
+        <v>0.8034359216690063</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>611398</v>
+        <v>204901</v>
       </c>
       <c r="Z4" t="n">
-        <v>8899088</v>
+        <v>2984316</v>
       </c>
       <c r="AA4" t="n">
-        <v>248302</v>
+        <v>83178</v>
       </c>
       <c r="AB4" t="n">
-        <v>16438</v>
+        <v>5500</v>
       </c>
       <c r="AC4" t="n">
-        <v>3432</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>654867</v>
+        <v>219464</v>
       </c>
       <c r="AG4" t="n">
-        <v>866780</v>
+        <v>290547</v>
       </c>
       <c r="AH4" t="n">
-        <v>396246</v>
+        <v>132613</v>
       </c>
       <c r="AI4" t="n">
-        <v>90074</v>
+        <v>30132</v>
       </c>
       <c r="AJ4" t="n">
-        <v>149506</v>
+        <v>49902</v>
       </c>
       <c r="AK4" t="n">
-        <v>39762</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571613669395447</v>
+        <v>0.9571695923805237</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106380939483643</v>
+        <v>0.9106889963150024</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579738140106201</v>
+        <v>0.8578088283538818</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6623735427856445</v>
+        <v>0.6621873378753662</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018570184707642</v>
+        <v>0.9018154144287109</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313915967941284</v>
+        <v>0.9313808679580688</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>65114</v>
+        <v>19456</v>
       </c>
       <c r="E5" t="n">
-        <v>729289</v>
+        <v>214032</v>
       </c>
       <c r="F5" t="n">
-        <v>1756383</v>
+        <v>641723</v>
       </c>
       <c r="G5" t="n">
-        <v>77153</v>
+        <v>20564</v>
       </c>
       <c r="H5" t="n">
-        <v>156059</v>
+        <v>36754</v>
       </c>
       <c r="I5" t="n">
-        <v>11285</v>
+        <v>1534</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1650318</v>
+        <v>401449</v>
       </c>
       <c r="L5" t="n">
-        <v>2224887</v>
+        <v>575908</v>
       </c>
       <c r="M5" t="n">
-        <v>1038903</v>
+        <v>292342</v>
       </c>
       <c r="N5" t="n">
-        <v>206659</v>
+        <v>68571</v>
       </c>
       <c r="O5" t="n">
-        <v>482175</v>
+        <v>137046</v>
       </c>
       <c r="P5" t="n">
-        <v>170952</v>
+        <v>52764</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999973773956299</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9288413524627686</v>
+        <v>0.945728063583374</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9044004678726196</v>
+        <v>0.9261307120323181</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9624700546264648</v>
+        <v>0.9692372679710388</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9908866286277771</v>
+        <v>0.9912099242210388</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9827086329460144</v>
+        <v>0.9857147932052612</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9949724674224854</v>
+        <v>0.9958110451698303</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>23984</v>
+        <v>8036</v>
       </c>
       <c r="Z5" t="n">
-        <v>254565</v>
+        <v>85188</v>
       </c>
       <c r="AA5" t="n">
-        <v>2397713</v>
+        <v>801097</v>
       </c>
       <c r="AB5" t="n">
-        <v>29795</v>
+        <v>9959</v>
       </c>
       <c r="AC5" t="n">
-        <v>87330</v>
+        <v>29152</v>
       </c>
       <c r="AD5" t="n">
-        <v>1899</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>639659</v>
+        <v>214567</v>
       </c>
       <c r="AG5" t="n">
-        <v>879774</v>
+        <v>294795</v>
       </c>
       <c r="AH5" t="n">
-        <v>397573</v>
+        <v>132968</v>
       </c>
       <c r="AI5" t="n">
-        <v>90282</v>
+        <v>30201</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150147</v>
+        <v>50108</v>
       </c>
       <c r="AK5" t="n">
-        <v>39800</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735750555992126</v>
+        <v>0.9735605120658875</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643478989601135</v>
+        <v>0.9643431901931763</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837958812713623</v>
+        <v>0.9838218092918396</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963183999061584</v>
+        <v>0.9963247179985046</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938832521438599</v>
+        <v>0.9939077496528625</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983758926391602</v>
+        <v>0.9983840584754944</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>36613</v>
+        <v>11523</v>
       </c>
       <c r="E6" t="n">
-        <v>57347</v>
+        <v>18238</v>
       </c>
       <c r="F6" t="n">
-        <v>83396</v>
+        <v>30998</v>
       </c>
       <c r="G6" t="n">
-        <v>60539</v>
+        <v>20763</v>
       </c>
       <c r="H6" t="n">
-        <v>27150</v>
+        <v>7449</v>
       </c>
       <c r="I6" t="n">
-        <v>2138</v>
+        <v>358</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>19318</v>
+        <v>6471</v>
       </c>
       <c r="Z6" t="n">
-        <v>16016</v>
+        <v>5370</v>
       </c>
       <c r="AA6" t="n">
-        <v>32584</v>
+        <v>10891</v>
       </c>
       <c r="AB6" t="n">
-        <v>176916</v>
+        <v>59133</v>
       </c>
       <c r="AC6" t="n">
-        <v>20921</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1443</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>337</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>42207</v>
+        <v>5808</v>
       </c>
       <c r="F7" t="n">
-        <v>240876</v>
+        <v>66541</v>
       </c>
       <c r="G7" t="n">
-        <v>138791</v>
+        <v>50792</v>
       </c>
       <c r="H7" t="n">
-        <v>1044761</v>
+        <v>372353</v>
       </c>
       <c r="I7" t="n">
-        <v>59913</v>
+        <v>13893</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2430</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>88798</v>
+        <v>29635</v>
       </c>
       <c r="AB7" t="n">
-        <v>22710</v>
+        <v>7591</v>
       </c>
       <c r="AC7" t="n">
-        <v>1376789</v>
+        <v>459291</v>
       </c>
       <c r="AD7" t="n">
-        <v>36126</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>1959</v>
+        <v>247</v>
       </c>
       <c r="F8" t="n">
-        <v>8504</v>
+        <v>1390</v>
       </c>
       <c r="G8" t="n">
-        <v>5142</v>
+        <v>1303</v>
       </c>
       <c r="H8" t="n">
-        <v>155227</v>
+        <v>49783</v>
       </c>
       <c r="I8" t="n">
-        <v>408894</v>
+        <v>140537</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>990</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>795</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>37688</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
